--- a/data/trans_bre/P1412-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P1412-Edad-trans_bre.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,99</t>
+          <t>0,0; 1,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 0,0</t>
+          <t>-0,76; 0,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 0,0</t>
+          <t>-1,3; 0,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-30,33%</t>
+          <t>-31,31%</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,78</t>
+          <t>0,0; 0,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,71</t>
+          <t>0,0; 0,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,27</t>
+          <t>-0,62; 0,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-0,36</t>
+          <t>-0,55</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-56,84%</t>
+          <t>-67,03%</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 0,0</t>
+          <t>-1,19; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 0,26</t>
+          <t>-1,73; 0,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 197,75</t>
+          <t>-100,0; 124,6</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>0,27</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>36,86%</t>
         </is>
       </c>
     </row>
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 1,81</t>
+          <t>-0,25; 1,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 0,26</t>
+          <t>-2,7; 0,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,99</t>
+          <t>-0,78; 1,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 72,73</t>
+          <t>-100,0; 73,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-72,2; 295,88</t>
+          <t>-64,54; 385,24</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-1,77</t>
+          <t>-1,2</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-72,07%</t>
+          <t>-51,33%</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 0,12</t>
+          <t>-5,13; -0,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 0,91</t>
+          <t>-3,24; 0,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,4; -0,44</t>
+          <t>-2,81; 0,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 59,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-87,93; 108,44</t>
+          <t>-87,4; 112,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-92,46; -24,19</t>
+          <t>-79,97; 19,51</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-2,14</t>
+          <t>-2,28</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-60,28%</t>
+          <t>-59,92%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 3,3</t>
+          <t>-3,48; 3,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 1,31</t>
+          <t>-3,48; 1,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,17; -0,63</t>
+          <t>-4,58; -0,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-56,04; 191,52</t>
+          <t>-55,8; 137,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-79,85; 123,34</t>
+          <t>-81,83; 94,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-82,5; -20,44</t>
+          <t>-83,04; -14,83</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-0,38</t>
+          <t>-0,36</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-43,8%</t>
+          <t>-39,28%</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,46</t>
+          <t>-0,4; 0,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 0,17</t>
+          <t>-0,61; 0,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,75; -0,03</t>
+          <t>-0,76; -0,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-45,22; 101,59</t>
+          <t>-45,05; 96,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-64,42; 38,21</t>
+          <t>-63,37; 35,44</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-65,69; -2,68</t>
+          <t>-62,68; -3,27</t>
         </is>
       </c>
     </row>
